--- a/settings.xlsx
+++ b/settings.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Common" sheetId="3" r:id="rId1"/>
